--- a/Rstudio/Dynamic chambers/Cattle Final NH3.xlsx
+++ b/Rstudio/Dynamic chambers/Cattle Final NH3.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzobenedetti/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzobenedetti/Documents/GitHub/Benedetti-2026-N2O-AgroscenaNext/Rstudio/Dynamic chambers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDF0EDF4-EE17-F34D-AB25-A2149EE205E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2E9E25-8B9A-EB45-AAFA-1A13FBEE3AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16600" xr2:uid="{1C17C28D-1FA2-AE49-AC6E-A2CF747B5228}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
   <si>
     <t>VALVE_ID</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>CSRAW</t>
+  </si>
+  <si>
+    <t>N-NH3 perc TAN</t>
   </si>
 </sst>
 </file>
@@ -455,13 +458,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{467644BA-9052-2C47-B92D-96324B4A9557}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,8 +475,11 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>4</v>
       </c>
@@ -482,8 +489,11 @@
       <c r="C2" s="3">
         <v>3.2982504650736675</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" s="3">
+        <v>9.6160260038063274</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>14</v>
       </c>
@@ -493,8 +503,11 @@
       <c r="C3" s="3">
         <v>3.7080232773527686</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3" s="3">
+        <v>10.810715752282016</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>17</v>
       </c>
@@ -504,8 +517,11 @@
       <c r="C4" s="3">
         <v>2.4937305125855955</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4" s="3">
+        <v>7.2704537479608211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>8</v>
       </c>
@@ -515,8 +531,11 @@
       <c r="C5" s="3">
         <v>2.3159966433127703</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D5" s="3">
+        <v>6.6370459361602077</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>12</v>
       </c>
@@ -526,8 +545,11 @@
       <c r="C6" s="3">
         <v>3.7250602908692567</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6" s="3">
+        <v>10.675057037259583</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>18</v>
       </c>
@@ -537,8 +559,11 @@
       <c r="C7" s="3">
         <v>3.5623815803567083</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D7" s="3">
+        <v>10.208862028892604</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>11</v>
       </c>
@@ -548,8 +573,11 @@
       <c r="C8" s="3">
         <v>5.0944412908455599</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D8" s="3">
+        <v>13.561591399241651</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>13</v>
       </c>
@@ -559,8 +587,11 @@
       <c r="C9" s="3">
         <v>5.6960246412389379</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D9" s="3">
+        <v>15.163028558853654</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>15</v>
       </c>
@@ -569,6 +600,9 @@
       </c>
       <c r="C10" s="3">
         <v>5.3870083815118628</v>
+      </c>
+      <c r="D10" s="3">
+        <v>14.340415830413523</v>
       </c>
     </row>
   </sheetData>

--- a/Rstudio/Dynamic chambers/Cattle Final NH3.xlsx
+++ b/Rstudio/Dynamic chambers/Cattle Final NH3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzobenedetti/Documents/GitHub/Benedetti-2026-N2O-AgroscenaNext/Rstudio/Dynamic chambers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2E9E25-8B9A-EB45-AAFA-1A13FBEE3AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFCEC558-2A15-8C43-964C-43E48E52F323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16600" xr2:uid="{1C17C28D-1FA2-AE49-AC6E-A2CF747B5228}"/>
   </bookViews>
@@ -490,7 +490,7 @@
         <v>3.2982504650736675</v>
       </c>
       <c r="D2" s="3">
-        <v>9.6160260038063274</v>
+        <v>10.400429257149124</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -504,7 +504,7 @@
         <v>3.7080232773527686</v>
       </c>
       <c r="D3" s="3">
-        <v>10.810715752282016</v>
+        <v>11.6798191811445</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -518,7 +518,7 @@
         <v>2.4937305125855955</v>
       </c>
       <c r="D4" s="3">
-        <v>7.2704537479608211</v>
+        <v>7.8538311758294217</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -532,7 +532,7 @@
         <v>2.3159966433127703</v>
       </c>
       <c r="D5" s="3">
-        <v>6.6370459361602077</v>
+        <v>7.2087937332059644</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -546,7 +546,7 @@
         <v>3.7250602908692567</v>
       </c>
       <c r="D6" s="3">
-        <v>10.675057037259583</v>
+        <v>11.58758250261207</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -560,7 +560,7 @@
         <v>3.5623815803567083</v>
       </c>
       <c r="D7" s="3">
-        <v>10.208862028892604</v>
+        <v>11.075102587534355</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -574,7 +574,7 @@
         <v>5.0944412908455599</v>
       </c>
       <c r="D8" s="3">
-        <v>13.561591399241651</v>
+        <v>14.715248426159382</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -588,7 +588,7 @@
         <v>5.6960246412389379</v>
       </c>
       <c r="D9" s="3">
-        <v>15.163028558853654</v>
+        <v>16.396869698333497</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -602,7 +602,7 @@
         <v>5.3870083815118628</v>
       </c>
       <c r="D10" s="3">
-        <v>14.340415830413523</v>
+        <v>15.545333774188622</v>
       </c>
     </row>
   </sheetData>
